--- a/tests/fixtures/ilo/isco08_en.xlsx
+++ b/tests/fixtures/ilo/isco08_en.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="ISCO-08 EN Struct and defin" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,28 +476,21 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Managers plan, direct, coordinate and evaluate the overall activities of enterprises, governments and other organizations, or of organizational units within them, and formulate and review their policies, laws, rules and regulations. Competent performance in most occupations in this major group requires skills at the fourth ISCO skill level, except for Sub-major group 14: Hospitality, Retail and Other Services Managers, for which skills at the third ISCO skill level are generally required.</t>
+          <t>Synthetic definition of ISCO-08 1 (not ILO text).</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tasks performed by managers usually include: formulating and advising on the policy, budgets, laws and regulations of enterprises, governments and other organizational units; establishing objectives and standards and formulating and evaluating programmes and policies and procedures for their implementation; ensuring appropriate systems and procedures are developed and implemented to provide budgetary control; authorising material, human and financial resources to implement policies and programmes; monitoring and evaluating performance of the organization or enterprise and of its staff; selecting or approving the selection of  staff; ensuring compliance with health and safety requirements; planning and directing daily operations; representing and negotiating on behalf of the government, enterprise or organizational unit managed in meetings and other forums.</t>
+          <t>Tasks include -
+(a)  synthetic task one of 1;
+(b)  synthetic task two of 1.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Occupations in this major group are classified into the following sub-major groups:
-11 Chief executives, Senior Officials and Legislators
-12 Administrative and Commercial Managers
-13 Production and Specialized Services Managers
-14 Hospitality, Retail and Other Services Managers</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>In distinguishing between managers classified in Major Group 1: Managers, and supervisors, classified in other major groups, it should be noted that both managers and supervisors may plan, organize, coordinate, control and direct the work done by others. In addition, managers usually have responsibility for and make decisions about: the overall strategic and operational direction of a business or organizational unit (for example about the kinds, quantity and quality of goods to be produced); budgets (how much money is to be spent and for what purposes); and the selection, appointment and dismissal of staff. Supervisors may provide advice and assistance to managers on these matters, especially in relation to staff selection and dismissal, but do not have authority to make decisions.
-It should be noted that it is not a necessary condition that managers have responsibility for all three of strategic and operational direction, budgets and staff selection and dismissal. The degree of autonomy they exercise may also vary. The critical difference is that supervisors are responsible only for the supervision of the activities of other workers, whereas managers have overall responsibility for the operations of an organizational unit.</t>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 1
+- Synthetic example B of 1</t>
         </is>
       </c>
     </row>
@@ -520,23 +512,23 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Chief executives, senior officials and legislators formulate and review the policies, and plan, direct, coordinate and evaluate the overall activities, of enterprises, governments and other organizations with the support of other managers. Competent performance in most occupations in this sub-major group requires skills at the fourth ISCO skill level.</t>
+          <t>Synthetic definition of ISCO-08 11 (not ILO text).</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tasks performed by workers in this sub-major group usually include: presiding over or participating in the proceedings of legislative bodies, boards of directors and committees; formulating and advising on the policy budgets, laws and regulations of enterprises, governments and other organizations; establishing objectives for enterprises, government departments or agencies and other organizations; formulating or approving and evaluating programmes and policies and  procedures for their implementation; ensuring appropriate systems and procedures are developed and implemented to provide budgetary control; authorizing material, human and financial resources to implement policies and programmmes; monitoring and evaluating performance of the organization or enterprise; selecting or approving the selection of senior staff; performing ceremonial duties and representing the enterprise, government, organization or community at official occasions and in meetings, negotiations, conventions and public hearings.</t>
+          <t>Tasks include -
+(a)  synthetic task one of 11;
+(b)  synthetic task two of 11.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Occupations in this sub-major group are classified into the following minor groups:
-111 Legislators and Senior Officials
-112 Managing Directors and Chief Executives</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 11
+- Synthetic example B of 11</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -556,25 +548,23 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Legislators and senior officials determine, formulate, advise on and direct the implementation of policies of national, state, regional or local governments or communities, and of special interest organizations. They make, ratify, amend or repeal laws, public rules and regulations and plan, organize, direct, control and evaluate the overall activities of government departments and agencies, traditional communities and special-interest organizations.</t>
+          <t>Synthetic definition of ISCO-08 111 (not ILO text).</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tasks performed usually include: presiding over or participating in the proceedings of legislative bodies and administrative councils of governments, legislative assemblies, local communities and special-interest organizations; serving on government administrative boards or official committees; investigating matters of concern to the public and promoting the interests of constituents; formulating and advising on government policy, budgets, laws and regulations; establishing objectives for organizations and formulating or approving and evaluating programmes and policies and  procedures for their implementation; recommending, reviewing, evaluating and approving documents, briefs and reports submitted; ensuring appropriate systems and procedures are developed and implemented to provide budgetary control; allocating the use of communal land and other resources; performing ceremonial duties and representing the government, organization or community at official occasions and in meetings, negotiations, conventions and public hearings.</t>
+          <t>Tasks include -
+(a)  synthetic task one of 111;
+(b)  synthetic task two of 111.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Occupations in this minor group are classified into the following unit groups:
-1111 Legislators
-1112 Senior Government Officials
-1113 Traditional Chiefs and Heads of Villages
-1114 Senior Officials of Special-interest Organizations</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 111
+- Synthetic example B of 111</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -594,138 +584,95 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Legislators determine, formulate, and direct policies of national, state, regional or local governments and international governmental agencies, and make, ratify, amend or repeal laws, public rules and regulations. They include elected and non-elected members of parliaments, councils and governments.</t>
+          <t>Synthetic definition of ISCO-08 1111 (not ILO text).</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Tasks include -
-(a)  presiding over or participating in the proceedings of legislative bodies and administrative councils of national, state, regional or local governments or legislative assemblies;
-(b)  determining, formulating and directing policies of national, state, regional or local governments;
-(c)  making, ratifying, amending or repealing laws, public rules and regulations within a statutory or constitutional framework;
-(d)  serving on government administrative boards or official committees;
-(e)  investigating matters of concern to the public and promoting the interests of the constituencies which they represent;
-(f)  attending community functions and meetings to provide service to the community, understand public opinion and provide information on government plans;
-(g)  negotiating with other legislators and representatives of interest groups in order to reconcile differing interests, and to create policies and agreements;
-(h)  as members of the government, directing senior administrators and officials of government departments and agencies in the interpretation and implementation of government policies.</t>
+(a)  synthetic task one of 1111;
+(b)  synthetic task two of 1111.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- City councillor
-- Government minister
-- Mayor
-- Member of parliament
-- President (government)
-- Secretary of State
-- Senator
-- State governor</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+- Synthetic example A of 1111
+- Synthetic example B of 1111</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finance Managers</t>
+          <t>Administrative and Commercial Managers</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Finance managers plan, direct and coordinate the financial operations of an enterprise or organization, in consultation with senior managers and with managers of other departments or sections, or of enterprises that provide financial services to other enterprises and organizations.</t>
+          <t>Synthetic definition of ISCO-08 12 (not ILO text).</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Tasks include -
-(a)  planning, directing and coordinating the financial operations of an enterprise or organization;
-(b)  assessing the financial situation of the enterprise or organization, preparing budgets and overseeing financial operations;
-(c)  consulting with the chief executive and with managers of other departments or sections
-(d)  establishing and managing budgets, controlling expenditure and ensuring the efficient use of resources;
-(e)  establishing and directing operational and administrative procedures;
-(f)  planning and directing daily operations;
-(g)  overseeing the selection, training and performance of staff;
-(h)  representing the enterprise or organization in dealings with outside bodies.</t>
+(a)  synthetic task one of 12;
+(b)  synthetic task two of 12.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- Company secretary
-- Finance manager</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
-- Financial institution branch manager - 1346
-- Financial controller - 2411
-- Management accountant - 2411</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+- Synthetic example A of 12
+- Synthetic example B of 12</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>121</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Management and Organization Analysts</t>
+          <t>Business Services and Administration Managers</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Management and organization analysts assist organizations to achieve greater efficiency and solve organizational problems. They study organizational structures, methods, systems and procedures.</t>
+          <t>Synthetic definition of ISCO-08 121 (not ILO text).</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(a)  assisting and encouraging the development of objectives, strategies and plans aimed at achieving customer satisfaction and the efficient use of organizations’ resources;
-(b)  analysing and evaluating current systems and structures;
-(c)  discussing current systems with staff and observing systems at all levels of organization;
-(d)  directing clients towards more efficient organization and developing solutions to organizational problems; 
-(e)  undertaking and reviewing work studies by analysing existing and proposed methods and procedures such as administrative and clerical procedures; 
-(f)  recording and analysing organizations’ workflow charts, records, reports, manuals and job descriptions;
-(g)  preparing and recommending proposals to revise methods and procedures, alter work flows, redefine job functions and resolve organizational problems; 
-(h)  assisting in implementing approved recommendations, issuing revised instructions and procedure manuals, and drafting other documentation; 
-(i)  reviewing operating procedures and advising of departures from procedures and standards.</t>
+          <t>Tasks include -
+(a)  synthetic task one of 121;
+(b)  synthetic task two of 121.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- Business consultant
-- Management consultant
-- Organization and methods analyst</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
-Business Analysts (IT) - 2511</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+- Synthetic example A of 121
+- Synthetic example B of 121</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -735,193 +682,141 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Systems Analysts</t>
+          <t>Finance Managers</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Systems analysts conduct research, analyse and evaluate client information technology requirements, procedures or problems, and develop and implement proposals, recommendations and plans to improve current or future information systems.</t>
+          <t>Synthetic definition of ISCO-08 1211 (not ILO text).</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Tasks include -
-(a)  consulting with users to formulate and document requirements and with management to ensure agreement on systems principles;
-(b)  identifying and analysing business processes, procedures and work practices;
-(c)  identifying and evaluating inefficiencies and recommending optimal business practices and system functionality and behaviour;
-(d)  taking responsibility for deploying functional solutions, such as creating, adopting and implementing system test plans;
-(e)  developing functional specifications for use by systems developers;
-(f)  expanding or modifying systems to improve workflow or serve new purposes;
-(g)  coordinating and linking the computer systems within an organization to increase compatibility.</t>
+(a)  synthetic task one of 1211;
+(b)  synthetic task two of 1211.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- Business analyst (IT)
-- Computer scientist
-- Information systems analyst
-- Systems consultant
-- Systems designer (IT)</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+- Synthetic example A of 1211
+- Synthetic example B of 1211</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Software Developers</t>
+          <t>Professionals</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Software developers research, analyse and evaluate requirements for existing or new software applications and operating systems, and design, develop, test and maintain software solutions to meet these requirements.</t>
+          <t>Synthetic definition of ISCO-08 2 (not ILO text).</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Tasks include -
-(a)   researching, analysing and evaluating requirements for software applications and operating systems;
-(b)  researching, designing, and developing computer software systems;
-(c)  consulting with engineering staff to evaluate interfaces between hardware and software;
-(d)  developing and directing software testing and validation procedures;
-(e)  modifying existing software to correct errors, to adapt it to new hardware or to upgrade interfaces and improve performance;
-(f)  directing software programming and development of documentation;
-(g)  assessing, developing, upgrading and documenting maintenance procedures for operating systems, communications environments and applications software;
-(h)  consulting with customers concerning maintenance of software system.</t>
+(a)  synthetic task one of 2;
+(b)  synthetic task two of 2.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- Programmer analyst
-- Software designer 
-- Software developer
-- Software engineer</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
-- Applications programmer -  2514</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+- Synthetic example A of 2
+- Synthetic example B of 2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2513</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Web and Multimedia Developers</t>
+          <t>Business and Administration Professionals</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Web and multimedia development professionals combine design and technical knowledge to research, analyse, evaluate, design, programme and modify websites and applications that draw together text, graphics, animations, imaging, audio and video displays and other interactive media.</t>
+          <t>Synthetic definition of ISCO-08 24 (not ILO text).</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Tasks include -
-(a)  analysing, designing and developing Internet sites by applying a mixture of artistry and creativity with software programming and scripting languages and interfacing with operating environments;
-(b)  designing and developing digital animations, imaging, presentations, games, audio and video clips, and Internet applications using multimedia software, tools and utilities, interactive graphics and programming languages;
-(c)  communicating with network specialists regarding web-related issues, such as security and hosting web sites, to control and enforce Internet and web server security, space allocation, user access, business continuity, web site backup and disaster recovery planning; 
-(d)  designing, developing and integrating computer code with other specialised inputs, such as image files, audio files and scripting languages, to produce, maintain and support web sites;
-(e)   assisting in analysing, specifying and developing Internet strategies, web-based methodologies and development plans.</t>
+(a)  synthetic task one of 24;
+(b)  synthetic task two of 24.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- Animation programmer
-- Computer games programmer
-- Internet developer 
-- Multimedia programmer
-- Website architect
-- Website developer</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
-- Website designer - 2166
-- Webmaster - 3514
-- Website administrator - 3514
-- Website technician-  3514</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+- Synthetic example A of 24
+- Synthetic example B of 24</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>242</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Applications Programmers</t>
+          <t>Administration Professionals</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Applications programmers write and maintain programmable code outlined in technical instructions and specifications for software applications and operating systems.</t>
+          <t>Synthetic definition of ISCO-08 242 (not ILO text).</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Tasks include -
-(a)  writing and maintaining programme code outlined in instructions and specifications in accordance with quality accredited standards;
-(b)  revising, repairing or expanding existing programmes to increase operating efficiency or adapt to new requirements;
-(c)  conducting trial runs of programmes and software applications to confirm that they will produce the desired information;
-(d)  compiling and writing documentation of programme development;
-(e)  identifying and communicating technical problems, processes and solutions.</t>
+(a)  synthetic task one of 242;
+(b)  synthetic task two of 242.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- Applications programmer</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
-- Programmer analyst - 2512
-- Software developer - 2512
-- Multimedia programmer - 2513</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+- Synthetic example A of 242
+- Synthetic example B of 242</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -931,157 +826,105 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Database Designers and Administrators</t>
+          <t>Management and Organization Analysts</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Database designers and administrators design, develop, control, maintain and support the optimal performance and security of databases.</t>
+          <t>Synthetic definition of ISCO-08 2421 (not ILO text).</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>Tasks include -
-(a)  designing and developing database architecture, data structures, tables, dictionaries and naming conventions for information systems projects;
-(b)  designing, constructing, modifying, integrating, implementing and testing database management systems;
-(c)  conducting research and providing advice on the selection, application and implementation of database management tools;
-(d)  developing and implementing data administration policy, documentation, standards and models;
-(e)  developing policies and procedures for database access and usage and for the backup and recovery of data;
-(f)  performing the operational establishment and preventive maintenance of backups, recovery procedures, and enforcing security and integrity controls.</t>
+(a)  synthetic task one of 2421;
+(b)  synthetic task two of 2421.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- Data administrator 
-- Database administrator  
-- Database analyst
-- Database architect</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
-- Network administrator - 2522
-- Systems administrator (computers) - 2522
-- Webmaster - 3514
-- Website administrator - 3514</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+- Synthetic example A of 2421
+- Synthetic example B of 2421</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Environmental and Occupational Health Inspectors and Associates</t>
+          <t>Information and Communications Technology Professionals</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Environmental and occupational health inspectors and associates investigate the implementation of rules and regulations relating to environmental factors that may affect human health, safety in the workplace, and safety of processes for the production of goods and services. They may implement and evaluate programmes to restore or improve safety and sanitary conditions under the supervision of a health professional.</t>
+          <t>Synthetic definition of ISCO-08 25 (not ILO text).</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>Tasks include -
-(a)  advising employers’ and workers’ representatives on the implementation of government and other rules and regulations concerning occupational safety and the working environment;
-(b)  inspecting places of work to ensure that the working environment, machinery and equipment conform to government and other rules, regulations and standards related to sanitation and/or occupational and environmental health and safety;
-(c)  giving advice on environmental sanitary problems and techniques;
-(d)  inspecting places of work and, by interviews, observations and other means, obtaining information about work practices and accidents to determine compliance with safety rules and regulations;
-(e)  inspecting areas of production, processing, transport, handling, storage and sale of products to ensure conformity with government and other rules, regulations and standards;
-(f)  advising enterprises and the general public on the implementation of government and other rules and regulations concerning hygiene, sanitation, purity and grading of primary products, food, drugs, cosmetics and similar goods;
-(g)  inspecting establishments to ensure that they conform to government and other rules and regulations concerning emission of pollutants and disposal of dangerous wastes;
-(h)  initiating action to maintain or improve hygiene and prevent pollution of water, air, food or soil;
-(i)  promoting preventive and corrective measures such as control of disease carrying organisms and of harmful substances in the air, hygienic food handling, proper disposal of waste and cleaning of public places;
-(j)  estimating quantities and costs of materials and labour required for health, safety and sanitation remediation projects;</t>
+(a)  synthetic task one of 25;
+(b)  synthetic task two of 25.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- Food sanitation and safety inspector
-- Health inspector
-- Occupational health and safety inspector
-- Pollution inspector
-- Production safety inspector
-- Sanitarian
-- Sanitary inspector</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
-- Environmental health officer - 2263
-- Occupational health and safety adviser - 2263
-- Occupational hygienist - 2263
-- Radiation protection expert - 2263</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+- Synthetic example A of 25
+- Synthetic example B of 25</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>251</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Accounting Associate Professionals</t>
+          <t>Software and Applications Developers and Analysts</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Accounting associate professionals maintain complete records of financial transactions of an undertaking and verify accuracy of documents and records relating to such transactions.</t>
+          <t>Synthetic definition of ISCO-08 251 (not ILO text).</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>Tasks include -
-(a)  maintaining complete records of all financial transactions of an undertaking according to general bookkeeping principles, with guidance from Accountants;
-(b)  verifying accuracy of documents and records relating to payments, receipts and other financial transactions;
-(c)  preparing financial statements and reports for specified periods;
-(d)  applying knowledge of bookkeeping principles and practices in order to identify and solve problems arising in the course of their work;
-(e)  using standard computer software packages to perform accounting and related calculations;
-(f)  supervising the work of accounts and bookkeeping clerks.</t>
+(a)  synthetic task one of 251;
+(b)  synthetic task two of 251.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Example of the occupations classified here:
-- Accounting Assistant
-- Bookkeeper</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
-- Accountant - 2411
-- Actuarial assistant - 3314
-- Bookkeeping clerk- 4311</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 251
+- Synthetic example B of 251</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1091,50 +934,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Administrative and Executive Secretaries</t>
+          <t>Systems Analysts</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Administrative and executive secretaries perform liaison, coordination and organizational tasks in support of managers and professionals and/or prepare correspondence, reports and records of proceedings and other specialized documentation.</t>
+          <t>Synthetic definition of ISCO-08 2511 (not ILO text).</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>Tasks include -
-(a)  drafting administrative correspondence and minutes;
-(b)  obtaining, proposing and monitoring deadlines and follow-up dates;
-(c)  screening requests for meetings, and scheduling and organizing meetings and travel arrangements;
-(d)  assisting in the preparation of budgets, monitoring of expenditures, drafting of contracts and purchasing or acquisition orders;
-(e)  liaising with other staff about a range of matters relating to the organization’s operations;
-(f)  writing and answering business or technical letters and other similar correspondence;
-(g)  preparing verbatim reports of proceedings in legislative assemblies, courts of law or other places using shorthand or specialized office equipment.
-(h)  supervising the work of  clerical support workers.</t>
+(a)  synthetic task one of 2511;
+(b)  synthetic task two of 2511.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Examples of the occupations classified here:
-- Administrative secretary
-- Correspondence assistant 
-- Court reporter
-- Executive assistant
-- Personal assistant </t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
-Medical transcriptionist - 3344
-Secretary (general) - 4120</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 2511
+- Synthetic example B of 2511</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1144,59 +970,33 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Legal and Related Associate Professionals</t>
+          <t>Software Developers</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Legal and related associate professionals perform support functions in courts of law or in law offices, provide services related to such legal matters as insurance contracts, the transferring of property and the granting of loans and other financial transactions or conduct investigations for clients.</t>
+          <t>Synthetic definition of ISCO-08 2512 (not ILO text).</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>Tasks include -
-(a)  documenting court proceedings and judgements;
-(b)  serving statements of claims, summonses, warrants, subpoenas and other court orders;
-(c)  maintaining order in court and hearing rooms;
-(d)  preparing legal documents including trial briefs, pleadings, appeals, wills and contracts and preparing, papers summarizing legal positions or setting out conditions of loans or insurance;
-(e)  investigating facts, assembling evidence and researching relevant statutes, decisions and other legal documents to prepare cases; 
-(f)  advising clients on legal matters;
-(g)  examining documentation such as mortgages, liens, judgements, easements, contracts and maps in order to verify properties’ legal descriptions and ownership;
-(h)  preparing documents relating to transfer of real estate, stocks or other matters requiring formal registration;
-(i)  investigating possible cases of theft of goods, money or information from business establishments and of other possible cases of unlawful behaviour by customers or employees; 
-(j)  investigating establishments or the circumstances and behaviour of persons on behalf of clients.</t>
+(a)  synthetic task one of 2512;
+(b)  synthetic task two of 2512.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- Bailiff
-- Conveyancing clerk
-- Court clerk
-- Judge’s clerk
-- Justice of the peace
-- Law clerk 
-- Legal assistant
-- Paralegal
-- Private detective 
-- Title searcher</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
-- Lawyer - 2611
-- Judge - 2612
-- Notary - 2619
-- Legal secretary - 3342</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+- Synthetic example A of 2512
+- Synthetic example B of 2512</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1206,47 +1006,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Information and Communications Technology Operations Technicians</t>
+          <t>Web and Multimedia Developers</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Information and communications technology operations technicians support the day-to-day processing, operation and monitoring of information and communications technology systems,  peripherlas, hardware, software and related computer equipment to ensure optimal performance and identify any problems.</t>
+          <t>Synthetic definition of ISCO-08 2513 (not ILO text).</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tasks include - 
-(a)  operating and controlling peripheral and related computer equipment;
-(b)  entering commands, using computer terminal, and activating controls on computer and peripheral equipment to integrate and operate equipment; 
-(c)  monitoring systems for equipment failure or errors in performance;
-(d)  notifying supervisor or maintenance technician of equipment malfunctions;
-(e)  responding to programme error messages by finding and correcting problems, escalating the problem to other staff or terminating the programme;
-(f)  reading job set-up instructions to determine equipment to be used, order of use, material such as disks and paper to be loaded, and control settings;
-(g)  retrieving, separating and sorting programme output as needed, and sending data to specified users;
-(h)  loading peripheral equipment, such as printers, with selected materials for operating runs, or overseeing loading of peripheral equipment by peripheral equipment operators.</t>
+          <t>Tasks include -
+(a)  synthetic task one of 2513;
+(b)  synthetic task two of 2513.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- Computer operator
-- Computer peripheral equipment operator
-- High-speed computer printer operator</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
-- Computer network technician - 3513</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+- Synthetic example A of 2513
+- Synthetic example B of 2513</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1256,93 +1042,67 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Computer Network and Systems Technicians</t>
+          <t>Applications Programmers</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Computer network and systems technicians establish, operate and maintain network and other data communications systems.</t>
+          <t>Synthetic definition of ISCO-08 2514 (not ILO text).</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>Tasks include -
-(a)  operating, maintaining and troubleshooting network systems;
-(b)  operating and maintaining data communications systems other than networks;
-(c)  assisting users with network and data communications problems;
-(d)  identifying areas needing upgraded equipment and software;
-(e)  installing computer hardware, network software, operating system software and applications software;
-(f)  performing start up and close down as well as backup and disaster recovery operations for computer networks.</t>
+(a)  synthetic task one of 2514;
+(b)  synthetic task two of 2514.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- Computer network technician
-- Network support technician</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
--  Network administrator - 2522
--  Network analyst - 2523
--  Computer operator - 3511
--  Web technician - 3514</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+- Synthetic example A of 2514
+- Synthetic example B of 2514</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>252</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>General Office Clerks</t>
+          <t>Database and Network Professionals</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>General office clerks perform a range of clerical and administrative tasks according to established procedures.</t>
+          <t>Synthetic definition of ISCO-08 252 (not ILO text).</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>Tasks include -
-(a)  recording, preparing, sorting, classifying and filing information;
-(b)  sorting, opening and sending mail;
-(c)  photocopying and faxing documents;
-(d)  preparing reports and correspondence of a routine nature;
-(e)  recording issue of equipment to staff;
-(f)  responding to telephone or electronic enquiries or forwarding to appropriate person;
-(g)  checking figures, preparing invoices and recording details of financial transactions made;
-(h)  transcribing information onto computers, and proofreading and correcting copy.</t>
+(a)  synthetic task one of 252;
+(b)  synthetic task two of 252.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- General office clerk 
-- Office clerk</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>In distinguishing the work of general office clerks from that of workers classified in Unit Group 4120: Secretaries (general), it should be noted that the work of secretaries is primarily concerned with the transcription, formatting and processing of correspondence and other documentation. Whilst general office clerks may perform some work of this nature, the transcription and processing of documentation is not the main focus of the work.</t>
+- Synthetic example A of 252
+- Synthetic example B of 252</t>
         </is>
       </c>
     </row>
@@ -1354,221 +1114,141 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Health Care Assistants</t>
+          <t>Database Designers and Administrators</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Health care assistants provide direct personal care and assistance with activities of daily living to patients and residents in a variety of health care settings such as hospitals, clinics and residential nursing care facilities. They generally work in implementation of established care plans and practices, and under the direct supervision of medical, nursing or other health professionals or associate professionals.</t>
+          <t>Synthetic definition of ISCO-08 2521 (not ILO text).</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>Tasks include -
-(a) providing care, support and treatment to patients and residents of medical, rehabilitative and residential care facilities according to treatment plans established by medical, nursing and other health professionals;
-(b)  assisting patients with personal and therapeutic care needs such as personal hygiene, feeding, dressing, physical mobility and exercise, communication, taking oral medications and changing dressings;
-(c)  positioning, lifting and turning patients and transporting them in wheelchairs or on movable beds;
-(d)  maintaining patients' environmental hygiene standards, such as cleaning patient rooms and changing bed linen;
-(e)  providing massage and other non-pharmacological pain relief measures, such as during pregnancy and labour;
-(f)  observing patients’ condition, responses and behaviour and reporting changes to a health professional.</t>
+(a)  synthetic task one of 2521;
+(b)  synthetic task two of 2521.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- Birth assistant (clinic or hospital)
-- Nursing aide (clinic or hospital)
-- Patient care assistant
-- Psychiatric aide</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
-- Nurse (professional) - 2221
-- Nurse (associate professional) - 3221
-- Ambulance worker - 3258
-- Nursing aide (home) - 5322</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Workers who provide personal care to residents of institutions and facilities that have permanent medical or nursing supervision (such as hospitals, rehabilitation centres, residential nursing care facilities and nursing homes), and therefore work under the direct supervision of nurses, medical doctors or other health professionals or associate professionals are classified in Unit Group 5321: Health Care Assistants. Workers who provide personal care to residents of independent living units, generally without permanent medical or nursing supervision, should be classified in Unit Group 5322: Home-based personal care workers. In general, workers classified in Minor Group 532: Personal Care Workers in Health Services, do not perform tasks requiring extensive medical knowledge or training, such as administering medications and cleaning and dressing wounds: where tasks of this type are performed they are of a simple and routine nature.</t>
+- Synthetic example A of 2521
+- Synthetic example B of 2521</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Home-based Personal Care Workers</t>
+          <t>Technicians and Associate Professionals</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Home-based personal care workers provide routine personal care and assistance with activities of daily living to persons who are in need of such care due to effects of ageing, illness, injury, or other physical or mental condition in private homes and other independent residential settings.</t>
+          <t>Synthetic definition of ISCO-08 3 (not ILO text).</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>Tasks include -
-(a)  assisting clients with personal and therapeutic care needs such as personal hygiene, feeding, dressing, physical mobility and exercise, communication, taking oral medications and changing dressings, usually as per care plans established by a health professional
-(b)  maintaining records of client care, changes in condition and responses to care and treatment, and reporting concerns or providing referrals to a health or social services professional; 
-(c)  positioning and lifting clients with physical mobility challenges, and helping transport them in wheelchairs and motor vehicles; 
-(d)  providing clients and families with emotional support and information and advice on topics such as nutrition, hygiene, exercise, caring for infants or adapting to disability or illness; 
-(e)  maintaining clients' environmental hygiene standards, such as changing bed linen, washing clothes and dishes, and cleaning living quarters; 
-(f)  providing psychological support to clients such as through conversation or reading aloud; 
-(g)  planning, purchasing, preparing, or serving meals to meet nutritional requirements and prescribed diets;
-(h)  providing support to parents and care for newborns during the postpartum period
-(i)  scheduling and accompanying clients for appointments with medical doctors and other health professionals or performing other errands.</t>
+(a)  synthetic task one of 3;
+(b)  synthetic task two of 3.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- Home birth assistant
-- Home care aide
-- Nursing aide (home)
-- Personal care provider</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
-- Nurse (professional) - 2221
-- Social worker (professional) - 2635
-- Nurse (associate professional) - 3221
-- Social worker (associate professional) - 3412
-- Nursing aide (clinic or hospital) - 5321</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Workers who provide personal care to residents of medical and health care facilities that have permanent medical or nursing supervision (such as in hospitals and nursing care homes), and therefore work under the direct supervision of health professionals or associate professionals, are classified in Unit Group 5321: Health Care Assistants. Workers who provide personal care in independent residential settings (including retirement communities with minimal or no on-site medical or nursing supervision), are classified in Unit Group 5322: Home-based Personal Care Workers. Home birth assistants, who provide emotional support and general care and advice to women and families during pregnancy and labour, but not delivery care to reduce health risks, are included here. Care workers who provide care and supervision for children in residential home and care centres are classified in Unit Group 5311: Child Care Workers.</t>
+- Synthetic example A of 3
+- Synthetic example B of 3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Crop Farm Labourers</t>
+          <t>Health Associate Professionals</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Crop farm labourers perform simple and routine tasks on farms in the production of crops such as fruit, nuts, grains and vegetables.</t>
+          <t>Synthetic definition of ISCO-08 32 (not ILO text).</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>Tasks include -
-(a)  digging and shovelling to clear ditches or for other purposes;
-(b)  loading and unloading supplies, produce and other materials;
-(c)  raking, pitching and stacking straw, hay and similar material;
-(d)  watering, thinning, and weeding crops by hand or using hand tools;
-(e)  picking fruit, nuts, vegetables and other crops;
-(f)  planting and harvesting field crops, such as rice, by hand;
-(g)  grading, sorting, bunching and packing produce into containers;
-(h)  performing minor repairs on fixtures, buildings, equipment and fences.</t>
+(a)  synthetic task one of 32;
+(b)  synthetic task two of 32.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- Cane planter
-- Fruit picker
-- Rice farm labourer
-- Vegetable picker</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
-- Skilled farm worker (field crops) - 6111
-- Construction labourer (building work) - 9313
-- Firewood collector - 9624
-- Water collector - 9624</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+- Synthetic example A of 32
+- Synthetic example B of 32</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9212</t>
+          <t>325</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Livestock Farm Labourers</t>
+          <t>Other Health Associate Professionals</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Livestock farm labourers perform simple and routine tasks in farm production of animals, including poultry and insects.</t>
+          <t>Synthetic definition of ISCO-08 325 (not ILO text).</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>Tasks include -
-(a)  digging and shovelling to clear ditches or for other purposes;
-(b)  loading and unloading supplies, produce and other materials;
-(c)  feeding, watering and cleaning animals and keeping their quarters clean;
-(d)  monitoring livestock and reporting on their condition;
-(e)  assisting with maintaining the health and welfare of livestock;
-(f)  assisting with herding, droving and separating livestock for milking, shearing, transportation or slaughter and between pastures;
-(g)  collecting eggs and placing in incubators;
-(h)  raking, pitching, stacking and storing hay, straw and other types of animal feed and bedding
-(i)  grading, sorting, packing produce into containers;
-(j)  performing minor repairs on fixtures, buildings, equipment and fences.</t>
+(a)  synthetic task one of 325;
+(b)  synthetic task two of 325.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- Livestock farm labourer</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
-- Drover - 6121
-- Shepherd – 6121
-- Skilled farm worker (livestock) - 6121
-- Firewood collector - 9624
-- Water collector - 9624</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+- Synthetic example A of 325
+- Synthetic example B of 325</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1578,155 +1258,105 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9213</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mixed Crop and Livestock Farm Labourers</t>
+          <t>Environmental and Occupational Health Inspectors and Associates</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mixed crop and livestock farm labourers perform simple and routine tasks in farm production of both crops and animals.</t>
+          <t>Synthetic definition of ISCO-08 3257 (not ILO text).</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>Tasks include -
-(a)  digging and shovelling to clear ditches or for other purposes;
-(b)  loading and unloading supplies, produce and other materials;
-(c)  raking, pitching and stacking straw, hay and similar material;
-(d)  watering, thinning and weeding crops by hand or using hand tools;
-(e)  picking fruit, nuts, vegetables and other crops and collecting eggs;
-(f)  planting and harvesting field crops, such as rice, by hand;
-(g)  feeding, watering, and cleaning animals and keeping their quarters clean;
-(h)  monitoring livestock, reporting on their condition;
-(i)  assisting with herding, droving and separating livestock for milking, shearing, transportation or slaughter, and between pastures;
-(j)  grading, sorting, bunching and packing produce into containers;
-(k)  performing minor repairs on fixtures, buildings, equipment and fences.</t>
+(a)  synthetic task one of 3257;
+(b)  synthetic task two of 3257.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- Farm labourer</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
-- Skilled farm worker (mixed farming) - 6130
-- Firewood collector - 9624
-- Water collector - 9624</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+- Synthetic example A of 3257
+- Synthetic example B of 3257</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Garden and Horticultural Labourers</t>
+          <t>Business and Administration Associate Professionals</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Garden and horticultural labourers perform simple and routine tasks in operations to cultivate and maintain trees, shrubs, flowers and other plants in parks and private gardens, to produce saplings, bulbs and seeds, or grow vegetables and flowers by intensive cultivation techniques.</t>
+          <t>Synthetic definition of ISCO-08 33 (not ILO text).</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>Tasks include -
-(a)  loading, unloading and moving supplies, produce and equipment;
-(b)  preparing garden sites and plots using hand tools and simple machines;
-(c)  assisting with planting and transplanting flowers, shrubs, trees and lawns;
-(d)  maintaining gardens by watering, weeding and mowing lawns;
-(e)  cleaning gardens and removing rubbish;
-(f)  assisting with propagating, planting and potting seeds, bulbs and cuttings;
-(g)  tending plants by hand watering and weeding;
-(h)  harvesting and packaging plants for sale and transport;
-(i)  performing minor repairs on fixtures, buildings, equipment and fences.</t>
+(a)  synthetic task one of 33;
+(b)  synthetic task two of 33.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- Garden labourer
-- Horticultural labourer
-- Lawn mower
-- Nursery labourer</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
-- Horticulturist - 6113
-- Landscape gardener - 6113
-- Market gardener - 6113
-- Crop farm labourer - 9211</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+- Synthetic example A of 33
+- Synthetic example B of 33</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>331</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Forestry Labourers</t>
+          <t>Financial and Mathematical Associate Professionals</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Forestry labourers perform simple and routine tasks to cultivate and maintain natural and plantation forests, and log, fell and saw trees.</t>
+          <t>Synthetic definition of ISCO-08 331 (not ILO text).</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>Tasks include -
-(a)  digging holes for tree planting;
-(b)  stacking and loading logs and timber;
-(c)  clearing undergrowth in forest stands and thinning young plantations;
-(d)  maintaining look-out for fires in forests;
-(e)  removing major branches and tree tops, trimming branches and sawing trunks into logs;
-(f)  operating and maintaining manual and hand-held machine saws to fell trees and cut felled trees and branches into logs;
-(g)  collecting seeds, and planting seedlings;
-(h)  performing minor repairs and maintenance of forest roads, buildings, facilities, and equipment.</t>
+(a)  synthetic task one of 331;
+(b)  synthetic task two of 331.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- Axeman/woman
-- Forestry labourer
-- Tree planter</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
-- Forestry worker (skilled) - 6210</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+- Synthetic example A of 331
+- Synthetic example B of 331</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1736,101 +1366,69 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>9216</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fishery and Aquaculture Labourers</t>
+          <t>Accounting Associate Professionals</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fishery and aquaculture labourers perform simple and routine tasks to cultivate, catch and harvest fish and seafood in aquaculture and inland, coastal and deep sea fishing operations.</t>
+          <t>Synthetic definition of ISCO-08 3313 (not ILO text).</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>Tasks include -
-(a)  cleaning the sea-bed and feeding fish and molluscs that are being cultivated;
-(b)  gathering seaweed, sea mosses, clams and other molluscs;
-(c)  preparing nets, lines and other fishing tackle and other deck equipment;
-(d)  operating fishing gear to catch fish and other marine life;
-(e)  cleaning, sorting and packing fish and seafood in ice and salt, and stowing catch in hold;
-(f)  cleaning deck surfaces and fish hold;
-(g)  handling mooring lines during docking.</t>
+(a)  synthetic task one of 3313;
+(b)  synthetic task two of 3313.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- Aquaculture labourer
-- Fishery labourer</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
-- Fish farmer - 6221
-- Coastal fishery skipper - 6222
-- Fisher (coastal waters) - 6222
-- Fisher (inland waters) - 6222
-- Deep-sea fisher - 6223</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+- Synthetic example A of 3313
+- Synthetic example B of 3313</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>9629</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Elementary Workers Not Elsewhere Classified</t>
+          <t>Administrative and Specialized Secretaries</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>This unit group covers elementary workers not classified elsewhere in Major Group 9: Elementary Occupations. For instance, the group includes those who issue and collect parking or admission tickets, provide personal items to patrons or customers in cloakrooms, and assist patrons at entertainment events.</t>
+          <t>Synthetic definition of ISCO-08 334 (not ILO text).</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>In such cases tasks would include -
-(a)  selling admission tickets and passes to patrons at entertainment events or collecting tickets, passes and tags from patrons;
-(b)  examining tickets or passes to verify authenticity, using criteria such as colour and date issued;
-(c)  guiding patrons to exits or providing other instructions or assistance in case of emergency;
-(d)  directing patrons to restrooms, concession stands and telephones;
-(e)  directing vehicle drivers to parking spaces;
-(f)  patrolling parking areas in order to prevent vehicle damage and vehicle property thefts;
-(g)  calculating parking charges and collecting fees from customers;
-(h)  assigning dressing room facilities, locker space or clothing containers to patrons of athletic or bathing establishments.</t>
+          <t>Tasks include -
+(a)  synthetic task one of 334;
+(b)  synthetic task two of 334.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>Examples of the occupations classified here:
-- Cloak room attendant
-- Fairground attendant
-- Parking attendant
-- Ticket collector
-- Usher</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Some related occupations classified elsewhere:
-- Parking valet - 8322</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+- Synthetic example A of 334
+- Synthetic example B of 334</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1840,73 +1438,1186 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>3343</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Administrative and Executive Secretaries</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 3343 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 3343;
+(b)  synthetic task two of 3343.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 3343
+- Synthetic example B of 3343</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Legal, Social, Cultural and Related Associate Professionals</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 34 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 34;
+(b)  synthetic task two of 34.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 34
+- Synthetic example B of 34</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Legal, Social and Religious Associate Professionals</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 341 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 341;
+(b)  synthetic task two of 341.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 341
+- Synthetic example B of 341</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>3411</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Legal and Related Associate Professionals</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 3411 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 3411;
+(b)  synthetic task two of 3411.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 3411
+- Synthetic example B of 3411</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Information and Communications Technicians</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 35 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 35;
+(b)  synthetic task two of 35.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 35
+- Synthetic example B of 35</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Information and Communications Technology Operations and User Support Technicians</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 351 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 351;
+(b)  synthetic task two of 351.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 351
+- Synthetic example B of 351</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>3511</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Information and Communications Technology Operations Technicians</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 3511 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 3511;
+(b)  synthetic task two of 3511.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 3511
+- Synthetic example B of 3511</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>3513</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Computer Network and Systems Technicians</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 3513 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 3513;
+(b)  synthetic task two of 3513.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 3513
+- Synthetic example B of 3513</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Clerical Support Workers</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 4 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 4;
+(b)  synthetic task two of 4.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 4
+- Synthetic example B of 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>General and Keyboard Clerks</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 41 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 41;
+(b)  synthetic task two of 41.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 41
+- Synthetic example B of 41</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>General Office Clerks</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 411 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 411;
+(b)  synthetic task two of 411.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 411
+- Synthetic example B of 411</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>4110</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>General Office Clerks</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 4110 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 4110;
+(b)  synthetic task two of 4110.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 4110
+- Synthetic example B of 4110</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Service and Sales Workers</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 5 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 5;
+(b)  synthetic task two of 5.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 5
+- Synthetic example B of 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Personal Care Workers</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 53 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 53;
+(b)  synthetic task two of 53.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 53
+- Synthetic example B of 53</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Personal Care Workers in Health Services</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 532 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 532;
+(b)  synthetic task two of 532.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 532
+- Synthetic example B of 532</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>5321</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Health Care Assistants</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 5321 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 5321;
+(b)  synthetic task two of 5321.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 5321
+- Synthetic example B of 5321</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>5322</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Home-based Personal Care Workers</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 5322 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 5322;
+(b)  synthetic task two of 5322.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 5322
+- Synthetic example B of 5322</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Elementary Occupations</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 9 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 9;
+(b)  synthetic task two of 9.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 9
+- Synthetic example B of 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Agricultural, Forestry and Fishery Labourers</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 92 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 92;
+(b)  synthetic task two of 92.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 92
+- Synthetic example B of 92</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Agricultural, Forestry and Fishery Labourers</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 921 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 921;
+(b)  synthetic task two of 921.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 921
+- Synthetic example B of 921</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Crop Farm Labourers</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 9211 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 9211;
+(b)  synthetic task two of 9211.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 9211
+- Synthetic example B of 9211</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>9212</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Livestock Farm Labourers</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 9212 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 9212;
+(b)  synthetic task two of 9212.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 9212
+- Synthetic example B of 9212</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>9213</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Mixed Crop and Livestock Farm Labourers</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 9213 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 9213;
+(b)  synthetic task two of 9213.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 9213
+- Synthetic example B of 9213</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>9214</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Garden and Horticultural Labourers</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 9214 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 9214;
+(b)  synthetic task two of 9214.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 9214
+- Synthetic example B of 9214</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>9215</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Forestry Labourers</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 9215 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 9215;
+(b)  synthetic task two of 9215.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 9215
+- Synthetic example B of 9215</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>9216</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Fishery and Aquaculture Labourers</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 9216 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 9216;
+(b)  synthetic task two of 9216.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 9216
+- Synthetic example B of 9216</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Refuse Workers and Other Elementary Workers</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 96 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 96;
+(b)  synthetic task two of 96.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 96
+- Synthetic example B of 96</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Other Elementary Workers</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 962 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 962;
+(b)  synthetic task two of 962.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 962
+- Synthetic example B of 962</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>9629</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Elementary Workers Not Elsewhere Classified</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 9629 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 9629;
+(b)  synthetic task two of 9629.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 9629
+- Synthetic example B of 9629</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Armed Forces Occupations</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 0 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 0;
+(b)  synthetic task two of 0.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 0
+- Synthetic example B of 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Commissioned Armed forces Officers</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 01 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 01;
+(b)  synthetic task two of 01.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 01
+- Synthetic example B of 01</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Commissioned Armed Forces Officers</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 011 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 011;
+(b)  synthetic task two of 011.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 011
+- Synthetic example B of 011</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>0110</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Commissioned Armed Forces Officers</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Commissioned armed forces officers provide leadership and management to organizational units in the armed forces and/or perform similar tasks to those performed in a variety of civilian occupations outside the armed forces. This group includes all members of the armed forces holding the rank of second lieutenant (or equivalent) or higher.</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Examples of the occupations classified here: 
-- Admiral
-- Air commodore
-- Air marshal
-- Brigadier (army)
-- Captain (air force)
-- Captain (army)
-- Captain (navy)
-- Colonel (army)
-- Field marshal
-- Flight Lieutenant (air force)
-- Flying officer (military)
-- General (army)
-- Group captain (air force)
-- Lieutenant (army)
-- Major (army)
-- Midshipman
-- Naval officer (military) 
-- Navy commander 
-- Officer cadet (armed forces)
-- Second lieutenant (army)
-- Squadron leader
-- Sublieutenant (navy)
-- Wing commander</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Excluded from this group are: 
- -  jobs held by persons in civilian employment of government establishments concerned with defence issues;
- -  police (other than military police);
- -  customs inspectors and members of border or other armed civilian services.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Synthetic definition of ISCO-08 0110 (not ILO text).</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Tasks include -
+(a)  synthetic task one of 0110;
+(b)  synthetic task two of 0110.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Examples of the occupations classified here:
+- Synthetic example A of 0110
+- Synthetic example B of 0110</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
